--- a/data/raw/PSY_adults.xlsx
+++ b/data/raw/PSY_adults.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giaco\Desktop\Git_META\META\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7694332B-FD43-405B-AB5A-9279242A2BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FD33B1-3764-44D3-B6BA-CB7CC74D50D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2115" yWindow="2115" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="61">
   <si>
     <t>ADHD</t>
   </si>
@@ -43,16 +43,10 @@
     <t>OCD</t>
   </si>
   <si>
-    <t>PTSD</t>
-  </si>
-  <si>
     <t>SCZ</t>
   </si>
   <si>
     <t>-0.09</t>
-  </si>
-  <si>
-    <t>-0.038</t>
   </si>
   <si>
     <t>-0.08</t>
@@ -64,25 +58,10 @@
     <t>-0.12</t>
   </si>
   <si>
-    <t>0.010</t>
-  </si>
-  <si>
-    <t>0.007</t>
-  </si>
-  <si>
     <t>0.01</t>
   </si>
   <si>
-    <t>0.023</t>
-  </si>
-  <si>
-    <t>-0.025</t>
-  </si>
-  <si>
     <t>-0.02</t>
-  </si>
-  <si>
-    <t>-0.009</t>
   </si>
   <si>
     <t>-0.019</t>
@@ -91,22 +70,10 @@
     <t>-0.17</t>
   </si>
   <si>
-    <t>-0.002</t>
-  </si>
-  <si>
-    <t>0.015</t>
-  </si>
-  <si>
     <t>-0.16</t>
   </si>
   <si>
-    <t>-0.036</t>
-  </si>
-  <si>
     <t>-0.13</t>
-  </si>
-  <si>
-    <t>-0.048</t>
   </si>
   <si>
     <t>-0.03</t>
@@ -118,28 +85,10 @@
     <t>-0.023</t>
   </si>
   <si>
-    <t>0.008</t>
-  </si>
-  <si>
-    <t>-0.034</t>
-  </si>
-  <si>
-    <t>0.006</t>
-  </si>
-  <si>
     <t>-0.04</t>
   </si>
   <si>
-    <t>0.057</t>
-  </si>
-  <si>
     <t>-0.1</t>
-  </si>
-  <si>
-    <t>-0.018</t>
-  </si>
-  <si>
-    <t>-0.005</t>
   </si>
   <si>
     <t>0.012</t>
@@ -148,82 +97,22 @@
     <t>-0.15</t>
   </si>
   <si>
-    <t>-0.046</t>
-  </si>
-  <si>
     <t>-0.05</t>
-  </si>
-  <si>
-    <t>-0.039</t>
   </si>
   <si>
     <t>-0.06</t>
   </si>
   <si>
-    <t>0.003</t>
-  </si>
-  <si>
-    <t>0.031</t>
-  </si>
-  <si>
     <t>0.02</t>
-  </si>
-  <si>
-    <t>0.087</t>
-  </si>
-  <si>
-    <t>0.030</t>
   </si>
   <si>
     <t>-0.11</t>
   </si>
   <si>
-    <t>0.027</t>
-  </si>
-  <si>
-    <t>0.000</t>
-  </si>
-  <si>
-    <t>-0.024</t>
-  </si>
-  <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>-0.045</t>
-  </si>
-  <si>
-    <t>0.043</t>
-  </si>
-  <si>
-    <t>-0.007</t>
-  </si>
-  <si>
-    <t>-0.047</t>
-  </si>
-  <si>
-    <t>0.046</t>
-  </si>
-  <si>
     <t>-0.07</t>
   </si>
   <si>
-    <t>0.009</t>
-  </si>
-  <si>
-    <t>-0.078</t>
-  </si>
-  <si>
     <t>-0.001</t>
-  </si>
-  <si>
-    <t>-0.043</t>
-  </si>
-  <si>
-    <t>-0.067</t>
-  </si>
-  <si>
-    <t>-0.051</t>
   </si>
   <si>
     <t>-0.01</t>
@@ -235,40 +124,7 @@
     <t>-0.18</t>
   </si>
   <si>
-    <t>0.052</t>
-  </si>
-  <si>
-    <t>0.026</t>
-  </si>
-  <si>
-    <t>0.037</t>
-  </si>
-  <si>
     <t>0.05</t>
-  </si>
-  <si>
-    <t>0.051</t>
-  </si>
-  <si>
-    <t>0.041</t>
-  </si>
-  <si>
-    <t>0.021</t>
-  </si>
-  <si>
-    <t>-0.040</t>
-  </si>
-  <si>
-    <t>-0.084</t>
-  </si>
-  <si>
-    <t>-0.056</t>
-  </si>
-  <si>
-    <t>-0.103</t>
-  </si>
-  <si>
-    <t>0.042</t>
   </si>
   <si>
     <t>-0.19</t>
@@ -344,6 +200,9 @@
   </si>
   <si>
     <t>0.11</t>
+  </si>
+  <si>
+    <t>PD</t>
   </si>
 </sst>
 </file>
@@ -676,10 +535,10 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -705,13 +564,13 @@
         <v>-0.7379</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D2" s="6">
         <v>-0.20699999999999999</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="6">
         <v>-5.8000000000000003E-2</v>
@@ -719,8 +578,8 @@
       <c r="G2" s="6">
         <v>-0.06</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>10</v>
+      <c r="H2" s="6">
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="I2" s="6">
         <v>-0.35199999999999998</v>
@@ -749,13 +608,13 @@
         <v>-6.5290000000000001E-2</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="D3" s="6">
         <v>-9.5000000000000001E-2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" s="6">
         <v>-4.2000000000000003E-2</v>
@@ -763,8 +622,8 @@
       <c r="G3" s="6">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>12</v>
+      <c r="H3" s="6">
+        <v>0.01</v>
       </c>
       <c r="I3" s="6">
         <v>-0.11899999999999999</v>
@@ -793,13 +652,13 @@
         <v>-0.75961999999999996</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="D4" s="6">
         <v>-0.26600000000000001</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" s="6">
         <v>-1.4E-2</v>
@@ -807,8 +666,8 @@
       <c r="G4" s="6">
         <v>-0.09</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>14</v>
+      <c r="H4" s="6">
+        <v>-0.05</v>
       </c>
       <c r="I4" s="6">
         <v>-0.36299999999999999</v>
@@ -837,13 +696,13 @@
         <v>-0.66256999999999999</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D5" s="6">
         <v>-5.6000000000000001E-2</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F5" s="6">
         <v>4.7E-2</v>
@@ -851,8 +710,8 @@
       <c r="G5" s="6">
         <v>-4.2000000000000003E-2</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>17</v>
+      <c r="H5" s="6">
+        <v>0.03</v>
       </c>
       <c r="I5" s="6">
         <v>-0.20300000000000001</v>
@@ -881,13 +740,13 @@
         <v>5.9735999999999997E-2</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="D6" s="6">
         <v>-3.5999999999999997E-2</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F6" s="6">
         <v>-4.1000000000000002E-2</v>
@@ -895,8 +754,8 @@
       <c r="G6" s="6">
         <v>-6.2E-2</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>20</v>
+      <c r="H6" s="6">
+        <v>-0.08</v>
       </c>
       <c r="I6" s="6">
         <v>-0.20300000000000001</v>
@@ -925,13 +784,13 @@
         <v>-0.53779999999999994</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="D7" s="6">
         <v>-0.28799999999999998</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F7" s="6">
         <v>-0.11700000000000001</v>
@@ -939,8 +798,8 @@
       <c r="G7" s="6">
         <v>-0.109</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>23</v>
+      <c r="H7" s="6">
+        <v>-0.09</v>
       </c>
       <c r="I7" s="6">
         <v>-0.49099999999999999</v>
@@ -969,13 +828,13 @@
         <v>-0.89488999999999996</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D8" s="6">
         <v>-0.26500000000000001</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F8" s="6">
         <v>-6.3E-2</v>
@@ -983,8 +842,8 @@
       <c r="G8" s="6">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>26</v>
+      <c r="H8" s="6">
+        <v>-0.05</v>
       </c>
       <c r="I8" s="6">
         <v>-0.36199999999999999</v>
@@ -1013,13 +872,13 @@
         <v>-0.53652</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D9" s="6">
         <v>-0.25</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F9" s="6">
         <v>-4.9000000000000002E-2</v>
@@ -1027,8 +886,8 @@
       <c r="G9" s="6">
         <v>-8.6999999999999994E-2</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>28</v>
+      <c r="H9" s="6">
+        <v>-0.1</v>
       </c>
       <c r="I9" s="6">
         <v>-0.44900000000000001</v>
@@ -1057,13 +916,13 @@
         <v>-0.62012</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D10" s="6">
         <v>-0.13200000000000001</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F10" s="6">
         <v>-0.104</v>
@@ -1071,8 +930,8 @@
       <c r="G10" s="6">
         <v>-6.8000000000000005E-2</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>30</v>
+      <c r="H10" s="6">
+        <v>0</v>
       </c>
       <c r="I10" s="6">
         <v>-0.309</v>
@@ -1101,13 +960,13 @@
         <v>-0.74733000000000005</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D11" s="6">
         <v>-0.156</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F11" s="6">
         <v>-2.3E-2</v>
@@ -1115,8 +974,8 @@
       <c r="G11" s="6">
         <v>-7.3999999999999996E-2</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>32</v>
+      <c r="H11" s="6">
+        <v>-0.02</v>
       </c>
       <c r="I11" s="6">
         <v>-0.33100000000000002</v>
@@ -1145,13 +1004,13 @@
         <v>-0.38435000000000002</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="D12" s="6">
         <v>-0.216</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F12" s="6">
         <v>-4.5999999999999999E-2</v>
@@ -1159,8 +1018,8 @@
       <c r="G12" s="6">
         <v>-9.6000000000000002E-2</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>33</v>
+      <c r="H12" s="6">
+        <v>-0.04</v>
       </c>
       <c r="I12" s="6">
         <v>-0.39800000000000002</v>
@@ -1189,13 +1048,13 @@
         <v>-0.51770000000000005</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D13" s="6">
         <v>-0.20799999999999999</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F13" s="6">
         <v>6.0000000000000001E-3</v>
@@ -1203,8 +1062,8 @@
       <c r="G13" s="6">
         <v>-5.1999999999999998E-2</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>18</v>
+      <c r="H13" s="6">
+        <v>0.03</v>
       </c>
       <c r="I13" s="6">
         <v>-0.34899999999999998</v>
@@ -1233,13 +1092,13 @@
         <v>-0.31744</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="D14" s="6">
         <v>-0.19900000000000001</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F14" s="6">
         <v>-0.13400000000000001</v>
@@ -1247,8 +1106,8 @@
       <c r="G14" s="6">
         <v>-8.4000000000000005E-2</v>
       </c>
-      <c r="H14" s="6" t="s">
-        <v>36</v>
+      <c r="H14" s="6">
+        <v>-0.02</v>
       </c>
       <c r="I14" s="6">
         <v>-0.23100000000000001</v>
@@ -1277,13 +1136,13 @@
         <v>-0.63039000000000001</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D15" s="6">
         <v>-0.252</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F15" s="6">
         <v>-0.09</v>
@@ -1291,8 +1150,8 @@
       <c r="G15" s="6">
         <v>-9.2999999999999999E-2</v>
       </c>
-      <c r="H15" s="6" t="s">
-        <v>38</v>
+      <c r="H15" s="6">
+        <v>-0.06</v>
       </c>
       <c r="I15" s="6">
         <v>-0.44400000000000001</v>
@@ -1321,13 +1180,13 @@
         <v>-0.18193999999999999</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="D16" s="6">
         <v>-2.1999999999999999E-2</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F16" s="6">
         <v>-7.1999999999999995E-2</v>
@@ -1335,8 +1194,8 @@
       <c r="G16" s="6">
         <v>-5.8999999999999997E-2</v>
       </c>
-      <c r="H16" s="6" t="s">
-        <v>39</v>
+      <c r="H16" s="6">
+        <v>0</v>
       </c>
       <c r="I16" s="6">
         <v>-0.27700000000000002</v>
@@ -1365,13 +1224,13 @@
         <v>-0.81562000000000001</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D17" s="6">
         <v>-0.13700000000000001</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F17" s="6">
         <v>-3.0000000000000001E-3</v>
@@ -1379,8 +1238,8 @@
       <c r="G17" s="6">
         <v>-1.2999999999999999E-2</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>20</v>
+      <c r="H17" s="6">
+        <v>-0.04</v>
       </c>
       <c r="I17" s="6">
         <v>-0.253</v>
@@ -1409,13 +1268,13 @@
         <v>-0.67005999999999999</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D18" s="6">
         <v>-0.29299999999999998</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F18" s="6">
         <v>-6.3E-2</v>
@@ -1423,8 +1282,8 @@
       <c r="G18" s="6">
         <v>-8.3000000000000004E-2</v>
       </c>
-      <c r="H18" s="6" t="s">
-        <v>44</v>
+      <c r="H18" s="6">
+        <v>-0.08</v>
       </c>
       <c r="I18" s="6">
         <v>-0.375</v>
@@ -1453,13 +1312,13 @@
         <v>-0.52405000000000002</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="D19" s="6">
         <v>-0.246</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F19" s="6">
         <v>-7.2999999999999995E-2</v>
@@ -1467,8 +1326,8 @@
       <c r="G19" s="6">
         <v>-0.05</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>46</v>
+      <c r="H19" s="6">
+        <v>-0.03</v>
       </c>
       <c r="I19" s="6">
         <v>-0.31900000000000001</v>
@@ -1497,13 +1356,13 @@
         <v>-0.52020999999999995</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D20" s="6">
         <v>-0.27</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F20" s="6">
         <v>-5.3999999999999999E-2</v>
@@ -1511,8 +1370,8 @@
       <c r="G20" s="6">
         <v>-3.2000000000000001E-2</v>
       </c>
-      <c r="H20" s="6" t="s">
-        <v>47</v>
+      <c r="H20" s="6">
+        <v>-0.01</v>
       </c>
       <c r="I20" s="6">
         <v>-0.34100000000000003</v>
@@ -1541,13 +1400,13 @@
         <v>-0.47924</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D21" s="6">
         <v>0.02</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F21" s="6">
         <v>9.4E-2</v>
@@ -1555,8 +1414,8 @@
       <c r="G21" s="6">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="H21" s="6" t="s">
-        <v>49</v>
+      <c r="H21" s="6">
+        <v>0.02</v>
       </c>
       <c r="I21" s="6">
         <v>-7.6999999999999999E-2</v>
@@ -1585,13 +1444,13 @@
         <v>-0.57374000000000003</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D22" s="6">
         <v>-9.6000000000000002E-2</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F22" s="6">
         <v>3.5999999999999997E-2</v>
@@ -1599,8 +1458,8 @@
       <c r="G22" s="6">
         <v>-2.3E-2</v>
       </c>
-      <c r="H22" s="6" t="s">
-        <v>36</v>
+      <c r="H22" s="6">
+        <v>-0.04</v>
       </c>
       <c r="I22" s="6">
         <v>-0.26100000000000001</v>
@@ -1629,13 +1488,13 @@
         <v>-0.69088000000000005</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D23" s="6">
         <v>-0.112</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F23" s="6">
         <v>-9.9000000000000005E-2</v>
@@ -1643,8 +1502,8 @@
       <c r="G23" s="6">
         <v>-7.0999999999999994E-2</v>
       </c>
-      <c r="H23" s="6" t="s">
-        <v>21</v>
+      <c r="H23" s="6">
+        <v>-0.02</v>
       </c>
       <c r="I23" s="6">
         <v>-0.29799999999999999</v>
@@ -1673,13 +1532,13 @@
         <v>-0.56516999999999995</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="D24" s="6">
         <v>-0.21099999999999999</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F24" s="6">
         <v>-0.02</v>
@@ -1687,8 +1546,8 @@
       <c r="G24" s="6">
         <v>-2.3E-2</v>
       </c>
-      <c r="H24" s="6" t="s">
-        <v>36</v>
+      <c r="H24" s="6">
+        <v>-0.05</v>
       </c>
       <c r="I24" s="6">
         <v>-0.34300000000000003</v>
@@ -1717,13 +1576,13 @@
         <v>-0.87892000000000003</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D25" s="6">
         <v>-0.20899999999999999</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F25" s="6">
         <v>-2.4E-2</v>
@@ -1731,8 +1590,8 @@
       <c r="G25" s="6">
         <v>-9.7000000000000003E-2</v>
       </c>
-      <c r="H25" s="6" t="s">
-        <v>54</v>
+      <c r="H25" s="6">
+        <v>-0.02</v>
       </c>
       <c r="I25" s="6">
         <v>-0.30099999999999999</v>
@@ -1761,13 +1620,13 @@
         <v>-8.2559999999999995E-2</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D26" s="6">
         <v>-0.153</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F26" s="6">
         <v>-0.13</v>
@@ -1775,8 +1634,8 @@
       <c r="G26" s="6">
         <v>-7.3999999999999996E-2</v>
       </c>
-      <c r="H26" s="6" t="s">
-        <v>34</v>
+      <c r="H26" s="6">
+        <v>0</v>
       </c>
       <c r="I26" s="6">
         <v>-0.182</v>
@@ -1805,13 +1664,13 @@
         <v>-0.53159999999999996</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="D27" s="6">
         <v>-0.27600000000000002</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F27" s="6">
         <v>-3.6999999999999998E-2</v>
@@ -1819,8 +1678,8 @@
       <c r="G27" s="6">
         <v>-9.5000000000000001E-2</v>
       </c>
-      <c r="H27" s="6" t="s">
-        <v>55</v>
+      <c r="H27" s="6">
+        <v>-0.01</v>
       </c>
       <c r="I27" s="6">
         <v>-0.36199999999999999</v>
@@ -1849,13 +1708,13 @@
         <v>-0.85841000000000001</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="D28" s="6">
         <v>-0.23300000000000001</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F28" s="6">
         <v>-6.6000000000000003E-2</v>
@@ -1863,8 +1722,8 @@
       <c r="G28" s="6">
         <v>-6.9000000000000006E-2</v>
       </c>
-      <c r="H28" s="6" t="s">
-        <v>57</v>
+      <c r="H28" s="6">
+        <v>-0.02</v>
       </c>
       <c r="I28" s="6">
         <v>-0.42499999999999999</v>
@@ -1893,13 +1752,13 @@
         <v>-0.89678999999999998</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="6">
         <v>-0.161</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F29" s="6">
         <v>-5.0000000000000001E-3</v>
@@ -1907,8 +1766,8 @@
       <c r="G29" s="6">
         <v>-6.2E-2</v>
       </c>
-      <c r="H29" s="6" t="s">
-        <v>47</v>
+      <c r="H29" s="6">
+        <v>0</v>
       </c>
       <c r="I29" s="6">
         <v>-0.20899999999999999</v>
@@ -1937,13 +1796,13 @@
         <v>-0.49138999999999999</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D30" s="6">
         <v>-0.20899999999999999</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F30" s="6">
         <v>1.2E-2</v>
@@ -1951,8 +1810,8 @@
       <c r="G30" s="6">
         <v>-7.0000000000000001E-3</v>
       </c>
-      <c r="H30" s="6" t="s">
-        <v>58</v>
+      <c r="H30" s="6">
+        <v>-0.06</v>
       </c>
       <c r="I30" s="6">
         <v>-0.44</v>
@@ -1981,13 +1840,13 @@
         <v>-0.81250999999999995</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="6">
         <v>-0.253</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F31" s="6">
         <v>-4.4999999999999998E-2</v>
@@ -1995,8 +1854,8 @@
       <c r="G31" s="6">
         <v>-5.1999999999999998E-2</v>
       </c>
-      <c r="H31" s="6" t="s">
-        <v>59</v>
+      <c r="H31" s="6">
+        <v>-0.05</v>
       </c>
       <c r="I31" s="6">
         <v>-0.39500000000000002</v>
@@ -2025,13 +1884,13 @@
         <v>-0.30835000000000001</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="D32" s="6">
         <v>-0.11799999999999999</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F32" s="6">
         <v>-1.0999999999999999E-2</v>
@@ -2039,8 +1898,8 @@
       <c r="G32" s="6">
         <v>-4.8000000000000001E-2</v>
       </c>
-      <c r="H32" s="6" t="s">
-        <v>26</v>
+      <c r="H32" s="6">
+        <v>-0.06</v>
       </c>
       <c r="I32" s="6">
         <v>-0.214</v>
@@ -2069,13 +1928,13 @@
         <v>0.110112</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="D33" s="6">
         <v>-0.11600000000000001</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F33" s="6">
         <v>1.2E-2</v>
@@ -2083,8 +1942,8 @@
       <c r="G33" s="6">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="H33" s="6" t="s">
-        <v>38</v>
+      <c r="H33" s="6">
+        <v>-0.06</v>
       </c>
       <c r="I33" s="6">
         <v>-0.246</v>
@@ -2113,13 +1972,13 @@
         <v>-0.18764</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="D34" s="6">
         <v>-0.12</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="F34" s="6">
         <v>-3.5000000000000003E-2</v>
@@ -2127,8 +1986,8 @@
       <c r="G34" s="6">
         <v>-4.0000000000000001E-3</v>
       </c>
-      <c r="H34" s="6" t="s">
-        <v>15</v>
+      <c r="H34" s="6">
+        <v>-0.06</v>
       </c>
       <c r="I34" s="6">
         <v>-0.253</v>
@@ -2157,13 +2016,13 @@
         <v>-0.23552000000000001</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="6">
         <v>-0.19800000000000001</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F35" s="6">
         <v>-0.111</v>
@@ -2171,8 +2030,8 @@
       <c r="G35" s="6">
         <v>-6.5000000000000002E-2</v>
       </c>
-      <c r="H35" s="6" t="s">
-        <v>38</v>
+      <c r="H35" s="6">
+        <v>-0.05</v>
       </c>
       <c r="I35" s="6">
         <v>-0.40799999999999997</v>
@@ -2201,13 +2060,13 @@
         <v>-0.64936000000000005</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D36" s="6">
         <v>-0.125</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F36" s="6">
         <v>-7.3999999999999996E-2</v>
@@ -2215,8 +2074,8 @@
       <c r="G36" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="H36" s="6" t="s">
-        <v>53</v>
+      <c r="H36" s="6">
+        <v>-0.09</v>
       </c>
       <c r="I36" s="6">
         <v>-0.35499999999999998</v>
@@ -2245,13 +2104,13 @@
         <v>-0.1439</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="D37" s="6">
         <v>-6.3E-2</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="F37" s="6">
         <v>-0.08</v>
@@ -2259,8 +2118,8 @@
       <c r="G37" s="6">
         <v>-3.7999999999999999E-2</v>
       </c>
-      <c r="H37" s="6" t="s">
-        <v>12</v>
+      <c r="H37" s="6">
+        <v>-0.04</v>
       </c>
       <c r="I37" s="6">
         <v>-0.152</v>
@@ -2289,13 +2148,13 @@
         <v>-0.66359000000000001</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="D38" s="6">
         <v>-0.20799999999999999</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F38" s="6">
         <v>6.0000000000000001E-3</v>
@@ -2303,8 +2162,8 @@
       <c r="G38" s="6">
         <v>-7.9000000000000001E-2</v>
       </c>
-      <c r="H38" s="6" t="s">
-        <v>62</v>
+      <c r="H38" s="6">
+        <v>-0.06</v>
       </c>
       <c r="I38" s="6">
         <v>-0.317</v>
@@ -2333,13 +2192,13 @@
         <v>-0.43959999999999999</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D39" s="6">
         <v>-2.9000000000000001E-2</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F39" s="6">
         <v>4.9000000000000002E-2</v>
@@ -2347,8 +2206,8 @@
       <c r="G39" s="6">
         <v>-3.3000000000000002E-2</v>
       </c>
-      <c r="H39" s="6" t="s">
-        <v>62</v>
+      <c r="H39" s="6">
+        <v>-0.01</v>
       </c>
       <c r="I39" s="6">
         <v>-0.22600000000000001</v>
@@ -2377,13 +2236,13 @@
         <v>4.1230000000000003E-2</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="D40" s="6">
         <v>-8.4000000000000005E-2</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F40" s="6">
         <v>-5.5E-2</v>
@@ -2391,8 +2250,8 @@
       <c r="G40" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="H40" s="6" t="s">
-        <v>63</v>
+      <c r="H40" s="6">
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="I40" s="6">
         <v>-0.15</v>
@@ -2421,13 +2280,13 @@
         <v>-0.50129999999999997</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="D41" s="6">
         <v>-0.26700000000000002</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F41" s="6">
         <v>-0.11600000000000001</v>
@@ -2435,8 +2294,8 @@
       <c r="G41" s="6">
         <v>-8.8999999999999996E-2</v>
       </c>
-      <c r="H41" s="6" t="s">
-        <v>56</v>
+      <c r="H41" s="6">
+        <v>-0.09</v>
       </c>
       <c r="I41" s="6">
         <v>-0.53600000000000003</v>
@@ -2465,13 +2324,13 @@
         <v>-0.88424999999999998</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D42" s="6">
         <v>-0.25800000000000001</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F42" s="6">
         <v>-4.1000000000000002E-2</v>
@@ -2479,8 +2338,8 @@
       <c r="G42" s="6">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="H42" s="6" t="s">
-        <v>42</v>
+      <c r="H42" s="6">
+        <v>0</v>
       </c>
       <c r="I42" s="6">
         <v>-0.34799999999999998</v>
@@ -2509,13 +2368,13 @@
         <v>-0.44220999999999999</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D43" s="6">
         <v>-0.189</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F43" s="6">
         <v>-0.11700000000000001</v>
@@ -2523,8 +2382,8 @@
       <c r="G43" s="6">
         <v>-5.8999999999999997E-2</v>
       </c>
-      <c r="H43" s="6" t="s">
-        <v>65</v>
+      <c r="H43" s="6">
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="I43" s="6">
         <v>-0.439</v>
@@ -2553,13 +2412,13 @@
         <v>-0.51597000000000004</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D44" s="6">
         <v>-0.183</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F44" s="6">
         <v>-7.0999999999999994E-2</v>
@@ -2567,8 +2426,8 @@
       <c r="G44" s="6">
         <v>-5.1999999999999998E-2</v>
       </c>
-      <c r="H44" s="6" t="s">
-        <v>66</v>
+      <c r="H44" s="6">
+        <v>0.04</v>
       </c>
       <c r="I44" s="6">
         <v>-0.308</v>
@@ -2597,13 +2456,13 @@
         <v>-0.65085999999999999</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D45" s="6">
         <v>-0.219</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F45" s="6">
         <v>5.0000000000000001E-3</v>
@@ -2611,8 +2470,8 @@
       <c r="G45" s="6">
         <v>-7.1999999999999995E-2</v>
       </c>
-      <c r="H45" s="6" t="s">
-        <v>57</v>
+      <c r="H45" s="6">
+        <v>-0.01</v>
       </c>
       <c r="I45" s="6">
         <v>-0.34200000000000003</v>
@@ -2641,13 +2500,13 @@
         <v>-0.38579000000000002</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="D46" s="6">
         <v>-0.20699999999999999</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F46" s="6">
         <v>-0.12</v>
@@ -2655,8 +2514,8 @@
       <c r="G46" s="6">
         <v>-0.108</v>
       </c>
-      <c r="H46" s="6" t="s">
-        <v>67</v>
+      <c r="H46" s="6">
+        <v>-0.04</v>
       </c>
       <c r="I46" s="6">
         <v>-0.35799999999999998</v>
@@ -2685,13 +2544,13 @@
         <v>-0.65175000000000005</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D47" s="6">
         <v>-0.19700000000000001</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="F47" s="6">
         <v>-1.2E-2</v>
@@ -2699,8 +2558,8 @@
       <c r="G47" s="6">
         <v>-4.3999999999999997E-2</v>
       </c>
-      <c r="H47" s="6" t="s">
-        <v>65</v>
+      <c r="H47" s="6">
+        <v>-0.01</v>
       </c>
       <c r="I47" s="6">
         <v>-0.38600000000000001</v>
@@ -2729,13 +2588,13 @@
         <v>-0.34704000000000002</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="D48" s="6">
         <v>-0.23</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F48" s="6">
         <v>-0.13100000000000001</v>
@@ -2743,8 +2602,8 @@
       <c r="G48" s="6">
         <v>-0.10199999999999999</v>
       </c>
-      <c r="H48" s="6" t="s">
-        <v>69</v>
+      <c r="H48" s="6">
+        <v>-0.03</v>
       </c>
       <c r="I48" s="6">
         <v>-0.24399999999999999</v>
@@ -2773,13 +2632,13 @@
         <v>-0.58730000000000004</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D49" s="6">
         <v>-0.219</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="F49" s="6">
         <v>-8.7999999999999995E-2</v>
@@ -2787,8 +2646,8 @@
       <c r="G49" s="6">
         <v>-9.8000000000000004E-2</v>
       </c>
-      <c r="H49" s="6" t="s">
-        <v>71</v>
+      <c r="H49" s="6">
+        <v>-0.1</v>
       </c>
       <c r="I49" s="6">
         <v>-0.379</v>
@@ -2817,13 +2676,13 @@
         <v>-0.21353</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="D50" s="6">
         <v>-8.5999999999999993E-2</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="F50" s="6">
         <v>-6.0999999999999999E-2</v>
@@ -2831,8 +2690,8 @@
       <c r="G50" s="6">
         <v>-0.08</v>
       </c>
-      <c r="H50" s="6" t="s">
-        <v>72</v>
+      <c r="H50" s="6">
+        <v>-0.05</v>
       </c>
       <c r="I50" s="6">
         <v>-0.28499999999999998</v>
@@ -2861,13 +2720,13 @@
         <v>-0.78946000000000005</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D51" s="6">
         <v>-0.14000000000000001</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F51" s="6">
         <v>-6.0000000000000001E-3</v>
@@ -2875,8 +2734,8 @@
       <c r="G51" s="6">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="H51" s="6" t="s">
-        <v>63</v>
+      <c r="H51" s="6">
+        <v>-0.05</v>
       </c>
       <c r="I51" s="6">
         <v>-0.216</v>
@@ -2905,13 +2764,13 @@
         <v>-0.61070000000000002</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D52" s="6">
         <v>-0.248</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="F52" s="6">
         <v>-1.7000000000000001E-2</v>
@@ -2919,8 +2778,8 @@
       <c r="G52" s="6">
         <v>-6.2E-2</v>
       </c>
-      <c r="H52" s="6" t="s">
-        <v>73</v>
+      <c r="H52" s="6">
+        <v>-0.04</v>
       </c>
       <c r="I52" s="6">
         <v>-0.42399999999999999</v>
@@ -2949,7 +2808,7 @@
         <v>-0.50185000000000002</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="D53" s="6">
         <v>-0.24099999999999999</v>
@@ -2963,8 +2822,8 @@
       <c r="G53" s="6">
         <v>-6.9000000000000006E-2</v>
       </c>
-      <c r="H53" s="6" t="s">
-        <v>60</v>
+      <c r="H53" s="6">
+        <v>-0.01</v>
       </c>
       <c r="I53" s="6">
         <v>-0.33900000000000002</v>
@@ -2993,13 +2852,13 @@
         <v>-0.62724000000000002</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D54" s="6">
         <v>-0.23100000000000001</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F54" s="6">
         <v>-3.1E-2</v>
@@ -3007,8 +2866,8 @@
       <c r="G54" s="6">
         <v>-5.6000000000000001E-2</v>
       </c>
-      <c r="H54" s="6" t="s">
-        <v>52</v>
+      <c r="H54" s="6">
+        <v>-0.06</v>
       </c>
       <c r="I54" s="6">
         <v>-0.373</v>
@@ -3037,13 +2896,13 @@
         <v>-0.21937999999999999</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D55" s="6">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="F55" s="6">
         <v>8.1000000000000003E-2</v>
@@ -3051,8 +2910,8 @@
       <c r="G55" s="6">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="H55" s="6" t="s">
-        <v>75</v>
+      <c r="H55" s="6">
+        <v>0.02</v>
       </c>
       <c r="I55" s="6">
         <v>-8.5999999999999993E-2</v>
@@ -3081,13 +2940,13 @@
         <v>-0.49118000000000001</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D56" s="6">
         <v>-7.4999999999999997E-2</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F56" s="6">
         <v>2.8000000000000001E-2</v>
@@ -3095,8 +2954,8 @@
       <c r="G56" s="6">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="H56" s="6" t="s">
-        <v>55</v>
+      <c r="H56" s="6">
+        <v>-0.08</v>
       </c>
       <c r="I56" s="6">
         <v>-0.28100000000000003</v>
@@ -3125,13 +2984,13 @@
         <v>-0.53813999999999995</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D57" s="6">
         <v>-0.16600000000000001</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F57" s="6">
         <v>-9.2999999999999999E-2</v>
@@ -3139,8 +2998,8 @@
       <c r="G57" s="6">
         <v>-5.7000000000000002E-2</v>
       </c>
-      <c r="H57" s="6" t="s">
-        <v>46</v>
+      <c r="H57" s="6">
+        <v>0</v>
       </c>
       <c r="I57" s="6">
         <v>-0.31</v>
@@ -3169,13 +3028,13 @@
         <v>-0.57991999999999999</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="D58" s="6">
         <v>-0.17899999999999999</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F58" s="6">
         <v>-2.1999999999999999E-2</v>
@@ -3183,8 +3042,8 @@
       <c r="G58" s="6">
         <v>-3.6999999999999998E-2</v>
       </c>
-      <c r="H58" s="6" t="s">
-        <v>76</v>
+      <c r="H58" s="6">
+        <v>-0.08</v>
       </c>
       <c r="I58" s="6">
         <v>-0.317</v>
@@ -3213,13 +3072,13 @@
         <v>-0.86197999999999997</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D59" s="6">
         <v>-0.188</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F59" s="6">
         <v>5.0000000000000001E-3</v>
@@ -3227,8 +3086,8 @@
       <c r="G59" s="6">
         <v>-0.10100000000000001</v>
       </c>
-      <c r="H59" s="6" t="s">
-        <v>65</v>
+      <c r="H59" s="6">
+        <v>-0.04</v>
       </c>
       <c r="I59" s="6">
         <v>-0.30399999999999999</v>
@@ -3257,13 +3116,13 @@
         <v>-2.7799999999999999E-3</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D60" s="6">
         <v>-8.6999999999999994E-2</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F60" s="6">
         <v>-9.8000000000000004E-2</v>
@@ -3271,8 +3130,8 @@
       <c r="G60" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="H60" s="6" t="s">
-        <v>21</v>
+      <c r="H60" s="6">
+        <v>-0.03</v>
       </c>
       <c r="I60" s="6">
         <v>-0.12</v>
@@ -3301,13 +3160,13 @@
         <v>-0.50651000000000002</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="D61" s="6">
         <v>-0.26400000000000001</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F61" s="6">
         <v>-3.7999999999999999E-2</v>
@@ -3315,8 +3174,8 @@
       <c r="G61" s="6">
         <v>-9.0999999999999998E-2</v>
       </c>
-      <c r="H61" s="6" t="s">
-        <v>50</v>
+      <c r="H61" s="6">
+        <v>0</v>
       </c>
       <c r="I61" s="6">
         <v>-0.313</v>
@@ -3345,13 +3204,13 @@
         <v>-0.72165000000000001</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="D62" s="6">
         <v>-0.25600000000000001</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F62" s="6">
         <v>-7.8E-2</v>
@@ -3359,8 +3218,8 @@
       <c r="G62" s="6">
         <v>-3.7999999999999999E-2</v>
       </c>
-      <c r="H62" s="6" t="s">
-        <v>77</v>
+      <c r="H62" s="6">
+        <v>-0.03</v>
       </c>
       <c r="I62" s="6">
         <v>-0.39700000000000002</v>
@@ -3389,13 +3248,13 @@
         <v>-0.92459999999999998</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D63" s="6">
         <v>-0.158</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F63" s="6">
         <v>3.2000000000000001E-2</v>
@@ -3403,8 +3262,8 @@
       <c r="G63" s="6">
         <v>-4.7E-2</v>
       </c>
-      <c r="H63" s="6" t="s">
-        <v>24</v>
+      <c r="H63" s="6">
+        <v>0</v>
       </c>
       <c r="I63" s="6">
         <v>-0.219</v>
@@ -3433,13 +3292,13 @@
         <v>-0.52170000000000005</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D64" s="6">
         <v>-0.19400000000000001</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F64" s="6">
         <v>-3.1E-2</v>
@@ -3447,8 +3306,8 @@
       <c r="G64" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="H64" s="6" t="s">
-        <v>78</v>
+      <c r="H64" s="6">
+        <v>-0.08</v>
       </c>
       <c r="I64" s="6">
         <v>-0.438</v>
@@ -3477,13 +3336,13 @@
         <v>-0.75641999999999998</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D65" s="6">
         <v>-0.184</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F65" s="6">
         <v>-5.2999999999999999E-2</v>
@@ -3491,8 +3350,8 @@
       <c r="G65" s="6">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="H65" s="6" t="s">
-        <v>79</v>
+      <c r="H65" s="6">
+        <v>-0.02</v>
       </c>
       <c r="I65" s="6">
         <v>-0.38600000000000001</v>
@@ -3521,13 +3380,13 @@
         <v>-0.33194000000000001</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="D66" s="6">
         <v>-0.10199999999999999</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F66" s="6">
         <v>-6.2E-2</v>
@@ -3535,8 +3394,8 @@
       <c r="G66" s="6">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="H66" s="6" t="s">
-        <v>80</v>
+      <c r="H66" s="6">
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="I66" s="6">
         <v>-0.20699999999999999</v>
@@ -3565,13 +3424,13 @@
         <v>-5.5140000000000002E-2</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="D67" s="6">
         <v>-5.8999999999999997E-2</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F67" s="6">
         <v>1.2999999999999999E-2</v>
@@ -3579,8 +3438,8 @@
       <c r="G67" s="6">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="H67" s="6" t="s">
-        <v>81</v>
+      <c r="H67" s="6">
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="I67" s="6">
         <v>-0.23599999999999999</v>
@@ -3609,13 +3468,13 @@
         <v>-0.25751000000000002</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="D68" s="6">
         <v>-0.109</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F68" s="6">
         <v>-5.0999999999999997E-2</v>
@@ -3623,8 +3482,8 @@
       <c r="G68" s="6">
         <v>-2.4E-2</v>
       </c>
-      <c r="H68" s="6" t="s">
-        <v>69</v>
+      <c r="H68" s="6">
+        <v>-0.04</v>
       </c>
       <c r="I68" s="6">
         <v>-0.26200000000000001</v>
@@ -3653,13 +3512,13 @@
         <v>-0.33905000000000002</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D69" s="6">
         <v>-0.16800000000000001</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F69" s="6">
         <v>-0.115</v>
@@ -3667,8 +3526,8 @@
       <c r="G69" s="6">
         <v>-6.5000000000000002E-2</v>
       </c>
-      <c r="H69" s="6" t="s">
-        <v>82</v>
+      <c r="H69" s="6">
+        <v>-0.05</v>
       </c>
       <c r="I69" s="6">
         <v>-0.40600000000000003</v>
@@ -3691,31 +3550,31 @@
     </row>
     <row r="70" spans="1:24" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="B70" s="6">
         <v>-0.32129999999999997</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="E70" s="6">
         <v>-0.04</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="H70" s="6">
-        <v>-6.3E-2</v>
+        <v>-0.01</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
@@ -3735,31 +3594,31 @@
     </row>
     <row r="71" spans="1:24" ht="15" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="B71" s="6">
         <v>-0.45513999999999999</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E71" s="6">
         <v>-0.04</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="H71" s="6">
-        <v>-7.4999999999999997E-2</v>
+        <v>-0.03</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
@@ -3779,31 +3638,31 @@
     </row>
     <row r="72" spans="1:24" ht="15" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B72" s="6">
         <v>-0.17862</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E72" s="6">
         <v>0.02</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="H72" s="6">
-        <v>4.0000000000000001E-3</v>
+        <v>-0.12</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
@@ -3823,31 +3682,31 @@
     </row>
     <row r="73" spans="1:24" ht="15" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="B73" s="6">
         <v>-0.41498000000000002</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="E73" s="6">
         <v>-0.08</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="H73" s="6">
-        <v>-0.17</v>
+        <v>-0.05</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
@@ -3867,31 +3726,31 @@
     </row>
     <row r="74" spans="1:24" ht="15" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="B74" s="6">
         <v>-0.24104</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E74" s="6">
         <v>-0.02</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="H74" s="6">
-        <v>4.1000000000000002E-2</v>
+        <v>-0.01</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
@@ -3911,31 +3770,31 @@
     </row>
     <row r="75" spans="1:24" ht="15" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B75" s="6">
         <v>-0.43703999999999998</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="E75" s="6">
         <v>0</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H75" s="6">
-        <v>1.4E-2</v>
+        <v>-0.03</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
@@ -3955,31 +3814,31 @@
     </row>
     <row r="76" spans="1:24" ht="15" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B76" s="6">
         <v>-0.63427</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E76" s="6">
         <v>-0.05</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="H76" s="6">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
@@ -3999,31 +3858,31 @@
     </row>
     <row r="77" spans="1:24" ht="15" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="B77" s="6">
         <v>-0.27438000000000001</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="E77" s="6">
         <v>-0.01</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="H77" s="6">
-        <v>-7.1999999999999995E-2</v>
+        <v>-0.06</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
@@ -4043,31 +3902,31 @@
     </row>
     <row r="78" spans="1:24" ht="15" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="B78" s="6">
         <v>-0.43391000000000002</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E78" s="6">
         <v>-0.08</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="H78" s="6">
-        <v>-0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
@@ -4087,31 +3946,31 @@
     </row>
     <row r="79" spans="1:24" ht="15" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B79" s="6">
         <v>-0.17760999999999999</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E79" s="6">
         <v>-0.01</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="H79" s="6">
-        <v>8.8999999999999999E-3</v>
+        <v>-0.09</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
@@ -4131,31 +3990,31 @@
     </row>
     <row r="80" spans="1:24" ht="15" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="B80" s="6">
         <v>-0.45106000000000002</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="E80" s="6">
         <v>-0.16</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="H80" s="6">
-        <v>-0.14000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
@@ -4175,31 +4034,31 @@
     </row>
     <row r="81" spans="1:24" ht="15" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="B81" s="6">
         <v>-0.35303000000000001</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E81" s="6">
         <v>-0.02</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="H81" s="6">
-        <v>2.8000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
@@ -4219,31 +4078,31 @@
     </row>
     <row r="82" spans="1:24" ht="15" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B82" s="6">
         <v>-0.40656999999999999</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="E82" s="6">
         <v>-0.01</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H82" s="6">
-        <v>1.0999999999999999E-2</v>
+        <v>-0.04</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
@@ -4263,31 +4122,31 @@
     </row>
     <row r="83" spans="1:24" ht="15" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B83" s="6">
         <v>-0.65678999999999998</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E83" s="6">
         <v>-0.09</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="H83" s="6">
-        <v>-6.3E-2</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
